--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.28680615176543</v>
+        <v>8.334105999661883</v>
       </c>
       <c r="D2" t="n">
-        <v>53.71735127206643</v>
+        <v>8.729069581710796</v>
       </c>
       <c r="E2" t="n">
-        <v>10.19285189026415</v>
+        <v>1.656338432167924</v>
       </c>
       <c r="F2" t="n">
-        <v>17.47490982155078</v>
+        <v>2.839672846002002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.62117760873114</v>
+        <v>4.32594136141881</v>
       </c>
       <c r="D3" t="n">
-        <v>27.87803676819454</v>
+        <v>4.530180974831612</v>
       </c>
       <c r="E3" t="n">
-        <v>10.19285189026415</v>
+        <v>1.656338432167924</v>
       </c>
       <c r="F3" t="n">
-        <v>17.47490982155078</v>
+        <v>2.839672846002002</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.60300547492442</v>
+        <v>5.785488389675219</v>
       </c>
       <c r="D4" t="n">
-        <v>11.24395484556088</v>
+        <v>1.827142662403642</v>
       </c>
       <c r="E4" t="n">
-        <v>10.19285189026415</v>
+        <v>1.656338432167924</v>
       </c>
       <c r="F4" t="n">
-        <v>17.47490982155078</v>
+        <v>2.839672846002002</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
